--- a/용어.xlsx
+++ b/용어.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GRS\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-STUDY\dev\workspace\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{073B4420-8BD9-46AB-8A96-70062B34C3CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358E35B2-334E-4936-9897-E51E3A91EE20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7800" yWindow="525" windowWidth="18045" windowHeight="13665" xr2:uid="{EE137B31-B5F9-40DD-BD99-D7A08D20373F}"/>
+    <workbookView xWindow="7020" yWindow="405" windowWidth="18045" windowHeight="13665" xr2:uid="{EE137B31-B5F9-40DD-BD99-D7A08D20373F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="49">
   <si>
     <t>파일명</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -173,12 +173,816 @@
   console.log(money.toLocaleString());</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>DB(데이터베이스)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DISTINCT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중복 없애는거임.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>DISTINCT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> BOOK_ID </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="14"/>
+        <color rgb="FF6C5151"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>SUB_RENTAL</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서브쿼리배울때(예전에도 배움)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서브쿼리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> BOOK_ID </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>IN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>DISTINCT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> BOOK_ID </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="14"/>
+        <color rgb="FF6C5151"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>SUB_RENTAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <t>결과가 여러행이나왔을때 비교를위해</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ANY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>PRICE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> &gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ALL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>PRICE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>SUB_BOOK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>CATEGORY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'IT'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>PRICE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> &gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ANY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>PRICE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>SUB_BOOK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>CATEGORY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'IT'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <t>&lt;foreach&gt;&lt;&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">    WHERE CART_NUM IN </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFD5B778"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">&lt;foreach </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>collection</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">="cartNumList" </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>item</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">="cartNum" </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>separator</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">="," </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>open</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">="(" </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>close</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=")"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFD5B778"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>#{cartNum}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFD5B778"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;/foreach&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>&lt;/delete&gt;</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;delete </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>="deleteCarts"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFD5B778"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DELETE FROM SHOP_CART</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,6 +997,68 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF800000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="14"/>
+      <color rgb="FF6C5151"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF006464"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF8E00C6"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF008000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFBCBEC4"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFD5B778"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF6AAB73"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -217,7 +1083,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -232,6 +1098,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -547,25 +1422,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13FAFE11-BEEB-4B66-8275-270748928941}">
-  <dimension ref="B3:J29"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="B3:J63"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="2" max="2" width="13.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="17.25" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.5" style="2" customWidth="1"/>
-    <col min="4" max="4" width="58.25" customWidth="1"/>
+    <col min="4" max="4" width="120.125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="34.625" customWidth="1"/>
     <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10">
       <c r="C3" s="3"/>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10">
       <c r="J6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10">
       <c r="B12" s="2" t="s">
         <v>4</v>
       </c>
@@ -585,7 +1460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10" ht="72" customHeight="1">
       <c r="B13" s="2" t="s">
         <v>2</v>
       </c>
@@ -602,7 +1477,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="2:10" ht="99" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:10" ht="99">
       <c r="B14" s="4" t="s">
         <v>12</v>
       </c>
@@ -619,7 +1494,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="2:10" ht="66" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:10" ht="66">
       <c r="B15" s="4" t="s">
         <v>16</v>
       </c>
@@ -636,12 +1511,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:10">
       <c r="B16" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:4">
       <c r="B17" s="2" t="s">
         <v>15</v>
       </c>
@@ -649,12 +1524,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="148.5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:4" ht="148.5">
       <c r="B18" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="2:4" ht="33" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:4" ht="33">
       <c r="B29" s="4" t="s">
         <v>25</v>
       </c>
@@ -663,6 +1538,122 @@
       </c>
       <c r="D29" s="1" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7">
+      <c r="B51" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7">
+      <c r="B52" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7" ht="18.75">
+      <c r="B53" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E53" t="s">
+        <v>30</v>
+      </c>
+      <c r="F53" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7" ht="18.75">
+      <c r="B54" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E54" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" ht="18.75">
+      <c r="B55" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7" ht="18.75">
+      <c r="B56" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7">
+      <c r="B57" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7">
+      <c r="D58" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7">
+      <c r="D59" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7">
+      <c r="D60" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7">
+      <c r="D61" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7">
+      <c r="D62" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7">
+      <c r="D63" s="6" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
